--- a/outputs/metrics/final_test_metrics_with_validation_threshold.xlsx
+++ b/outputs/metrics/final_test_metrics_with_validation_threshold.xlsx
@@ -508,40 +508,40 @@
         <v>0.5</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7166123778501629</v>
+        <v>0.7019543973941368</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6336336336336337</v>
+        <v>0.6626016260162602</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8022813688212928</v>
+        <v>0.6197718631178707</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3663663663663664</v>
+        <v>0.3373983739837398</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7080536912751678</v>
+        <v>0.6404715127701375</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6524216524216524</v>
+        <v>0.7635327635327636</v>
       </c>
       <c r="J2" t="n">
-        <v>0.548051948051948</v>
+        <v>0.4710982658959538</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7867093475458495</v>
+        <v>0.7777398632911942</v>
       </c>
       <c r="L2" t="n">
-        <v>229</v>
+        <v>268</v>
       </c>
       <c r="M2" t="n">
-        <v>122</v>
+        <v>83</v>
       </c>
       <c r="N2" t="n">
-        <v>52</v>
+        <v>100</v>
       </c>
       <c r="O2" t="n">
-        <v>211</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3">
@@ -556,43 +556,43 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.49</v>
+        <v>0.39</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7149837133550488</v>
+        <v>0.7182410423452769</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6301775147928994</v>
+        <v>0.6461038961038961</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8098859315589354</v>
+        <v>0.7566539923954373</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3698224852071006</v>
+        <v>0.3538961038961039</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7088186356073212</v>
+        <v>0.6970227670753065</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6438746438746439</v>
+        <v>0.6894586894586895</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5489690721649485</v>
+        <v>0.5349462365591398</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7867093475458495</v>
+        <v>0.7777398632911942</v>
       </c>
       <c r="L3" t="n">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="M3" t="n">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="N3" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="O3" t="n">
-        <v>213</v>
+        <v>199</v>
       </c>
     </row>
     <row r="4">
@@ -607,43 +607,43 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.49</v>
+        <v>0.39</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7149837133550488</v>
+        <v>0.7182410423452769</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6301775147928994</v>
+        <v>0.6461038961038961</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8098859315589354</v>
+        <v>0.7566539923954373</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3698224852071006</v>
+        <v>0.3538961038961039</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7088186356073212</v>
+        <v>0.6970227670753065</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6438746438746439</v>
+        <v>0.6894586894586895</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5489690721649485</v>
+        <v>0.5349462365591398</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7867093475458495</v>
+        <v>0.7777398632911942</v>
       </c>
       <c r="L4" t="n">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="M4" t="n">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="N4" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="O4" t="n">
-        <v>213</v>
+        <v>199</v>
       </c>
     </row>
     <row r="5">
@@ -658,43 +658,43 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.46</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7263843648208469</v>
+        <v>0.7100977198697068</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6655052264808362</v>
+        <v>0.6568265682656826</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7262357414448669</v>
+        <v>0.6768060836501901</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3344947735191638</v>
+        <v>0.3431734317343174</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6945454545454546</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7264957264957265</v>
+        <v>0.7350427350427351</v>
       </c>
       <c r="J5" t="n">
-        <v>0.532033426183844</v>
+        <v>0.5</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7867093475458495</v>
+        <v>0.7777398632911942</v>
       </c>
       <c r="L5" t="n">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="M5" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="N5" t="n">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="O5" t="n">
-        <v>191</v>
+        <v>178</v>
       </c>
     </row>
     <row r="6">
@@ -712,40 +712,40 @@
         <v>0.5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6775244299674267</v>
+        <v>0.6889250814332247</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6254826254826255</v>
+        <v>0.6046511627906976</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6159695817490495</v>
+        <v>0.7908745247148289</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3745173745173745</v>
+        <v>0.3953488372093023</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6206896551724138</v>
+        <v>0.685337726523888</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7236467236467237</v>
+        <v>0.6125356125356125</v>
       </c>
       <c r="J6" t="n">
-        <v>0.45</v>
+        <v>0.5213032581453634</v>
       </c>
       <c r="K6" t="n">
-        <v>0.753772491415077</v>
+        <v>0.7554840596665692</v>
       </c>
       <c r="L6" t="n">
-        <v>254</v>
+        <v>215</v>
       </c>
       <c r="M6" t="n">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="N6" t="n">
-        <v>101</v>
+        <v>55</v>
       </c>
       <c r="O6" t="n">
-        <v>162</v>
+        <v>208</v>
       </c>
     </row>
     <row r="7">
@@ -760,43 +760,43 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.51</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6856677524429967</v>
+        <v>0.6840390879478827</v>
       </c>
       <c r="E7" t="n">
-        <v>0.64</v>
+        <v>0.6161616161616161</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6083650190114068</v>
+        <v>0.6958174904942965</v>
       </c>
       <c r="G7" t="n">
-        <v>0.36</v>
+        <v>0.3838383838383838</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6237816764132553</v>
+        <v>0.6535714285714286</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7435897435897436</v>
+        <v>0.6752136752136753</v>
       </c>
       <c r="J7" t="n">
-        <v>0.453257790368272</v>
+        <v>0.4854111405835544</v>
       </c>
       <c r="K7" t="n">
-        <v>0.753772491415077</v>
+        <v>0.7554840596665692</v>
       </c>
       <c r="L7" t="n">
-        <v>261</v>
+        <v>237</v>
       </c>
       <c r="M7" t="n">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="N7" t="n">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="O7" t="n">
-        <v>160</v>
+        <v>183</v>
       </c>
     </row>
     <row r="8">
@@ -811,43 +811,43 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.51</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6856677524429967</v>
+        <v>0.6840390879478827</v>
       </c>
       <c r="E8" t="n">
-        <v>0.64</v>
+        <v>0.6161616161616161</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6083650190114068</v>
+        <v>0.6958174904942965</v>
       </c>
       <c r="G8" t="n">
-        <v>0.36</v>
+        <v>0.3838383838383838</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6237816764132553</v>
+        <v>0.6535714285714286</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7435897435897436</v>
+        <v>0.6752136752136753</v>
       </c>
       <c r="J8" t="n">
-        <v>0.453257790368272</v>
+        <v>0.4854111405835544</v>
       </c>
       <c r="K8" t="n">
-        <v>0.753772491415077</v>
+        <v>0.7554840596665692</v>
       </c>
       <c r="L8" t="n">
-        <v>261</v>
+        <v>237</v>
       </c>
       <c r="M8" t="n">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="N8" t="n">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="O8" t="n">
-        <v>160</v>
+        <v>183</v>
       </c>
     </row>
     <row r="9">
@@ -862,43 +862,43 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.53</v>
+        <v>0.61</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6872964169381107</v>
+        <v>0.6921824104234527</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6485355648535565</v>
+        <v>0.64453125</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5893536121673004</v>
+        <v>0.6273764258555133</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3514644351464435</v>
+        <v>0.35546875</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6175298804780877</v>
+        <v>0.6358381502890174</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7606837606837606</v>
+        <v>0.7407407407407407</v>
       </c>
       <c r="J9" t="n">
-        <v>0.446685878962536</v>
+        <v>0.4661016949152542</v>
       </c>
       <c r="K9" t="n">
-        <v>0.753772491415077</v>
+        <v>0.7554840596665692</v>
       </c>
       <c r="L9" t="n">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="M9" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="N9" t="n">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="O9" t="n">
-        <v>155</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10">
@@ -916,40 +916,40 @@
         <v>0.5</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6921824104234527</v>
+        <v>0.6872964169381107</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6163522012578616</v>
+        <v>0.6085626911314985</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7452471482889734</v>
+        <v>0.7566539923954373</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3836477987421384</v>
+        <v>0.3914373088685015</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6746987951807228</v>
+        <v>0.6745762711864407</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6524216524216524</v>
+        <v>0.6353276353276354</v>
       </c>
       <c r="J10" t="n">
-        <v>0.509090909090909</v>
+        <v>0.5089514066496164</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7768028338370544</v>
+        <v>0.7648868523393239</v>
       </c>
       <c r="L10" t="n">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="M10" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="N10" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="O10" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11">
@@ -964,43 +964,43 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6970684039087948</v>
+        <v>0.6954397394136808</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6305084745762712</v>
+        <v>0.625</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7072243346007605</v>
+        <v>0.7224334600760456</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3694915254237288</v>
+        <v>0.375</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6701940035273368</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6894586894586895</v>
+        <v>0.6752136752136753</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5</v>
+        <v>0.5039787798408488</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7768028338370544</v>
+        <v>0.7648868523393239</v>
       </c>
       <c r="L11" t="n">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="M11" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="N11" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="O11" t="n">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12">
@@ -1015,43 +1015,43 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6970684039087948</v>
+        <v>0.6954397394136808</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6305084745762712</v>
+        <v>0.625</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7072243346007605</v>
+        <v>0.7224334600760456</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3694915254237288</v>
+        <v>0.375</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6701940035273368</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6894586894586895</v>
+        <v>0.6752136752136753</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5</v>
+        <v>0.5039787798408488</v>
       </c>
       <c r="K12" t="n">
-        <v>0.7768028338370544</v>
+        <v>0.7648868523393239</v>
       </c>
       <c r="L12" t="n">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="M12" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="N12" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="O12" t="n">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="13">
@@ -1066,43 +1066,43 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.52</v>
+        <v>0.58</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6970684039087948</v>
+        <v>0.7100977198697068</v>
       </c>
       <c r="E13" t="n">
-        <v>0.6305084745762712</v>
+        <v>0.6615969581749049</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7072243346007605</v>
+        <v>0.6615969581749049</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3694915254237288</v>
+        <v>0.3384030418250951</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6615969581749049</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6894586894586895</v>
+        <v>0.7464387464387464</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5</v>
+        <v>0.4943181818181818</v>
       </c>
       <c r="K13" t="n">
-        <v>0.7768028338370544</v>
+        <v>0.7648868523393239</v>
       </c>
       <c r="L13" t="n">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="M13" t="n">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="N13" t="n">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="O13" t="n">
-        <v>186</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
